--- a/tests/fixtures/ctpe_shape/batch2/has_the_finding/b2_has.xlsx
+++ b/tests/fixtures/ctpe_shape/batch2/has_the_finding/b2_has.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2022-05-07 11:10:00</t>
+          <t>2031-02-03 04:05:00</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44688.46527777778</v>
+        <v>47882.17013888889</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
